--- a/output/xlsx/eoss-403.xlsx
+++ b/output/xlsx/eoss-403.xlsx
@@ -2784,7 +2784,7 @@
         <v>46193.30662538194</v>
       </c>
       <c r="D2" s="1">
-        <v>46193.556597222225</v>
+        <v>46193.306597222225</v>
       </c>
       <c r="E2">
         <v>863</v>
@@ -2870,7 +2870,7 @@
         <v>46193.306973321756</v>
       </c>
       <c r="D3" s="1">
-        <v>46193.55694444444</v>
+        <v>46193.30694444444</v>
       </c>
       <c r="E3">
         <v>870</v>
@@ -2980,7 +2980,7 @@
         <v>46193.307323229164</v>
       </c>
       <c r="D4" s="1">
-        <v>46193.557291666664</v>
+        <v>46193.307291666664</v>
       </c>
       <c r="E4">
         <v>1444</v>
@@ -3102,7 +3102,7 @@
         <v>46193.30766658565</v>
       </c>
       <c r="D5" s="1">
-        <v>46193.55763888889</v>
+        <v>46193.30763888889</v>
       </c>
       <c r="E5">
         <v>2011</v>
@@ -3224,7 +3224,7 @@
         <v>46193.30801428241</v>
       </c>
       <c r="D6" s="1">
-        <v>46193.55798611111</v>
+        <v>46193.30798611111</v>
       </c>
       <c r="E6">
         <v>2618</v>
@@ -3346,7 +3346,7 @@
         <v>46193.30871188657</v>
       </c>
       <c r="D7" s="1">
-        <v>46193.55868055556</v>
+        <v>46193.30868055556</v>
       </c>
       <c r="E7">
         <v>3770</v>
@@ -3468,7 +3468,7 @@
         <v>46193.309056342594</v>
       </c>
       <c r="D8" s="1">
-        <v>46193.55902777778</v>
+        <v>46193.30902777778</v>
       </c>
       <c r="E8">
         <v>4374</v>
@@ -3590,7 +3590,7 @@
         <v>46193.30940306713</v>
       </c>
       <c r="D9" s="1">
-        <v>46193.559375</v>
+        <v>46193.309375</v>
       </c>
       <c r="E9">
         <v>4958</v>
@@ -3712,7 +3712,7 @@
         <v>46193.309754305556</v>
       </c>
       <c r="D10" s="1">
-        <v>46193.55972222222</v>
+        <v>46193.30972222222</v>
       </c>
       <c r="E10">
         <v>5453</v>
@@ -3834,7 +3834,7 @@
         <v>46193.31009755787</v>
       </c>
       <c r="D11" s="1">
-        <v>46193.560069444444</v>
+        <v>46193.310069444444</v>
       </c>
       <c r="E11">
         <v>6067</v>
@@ -3956,7 +3956,7 @@
         <v>46193.31044528935</v>
       </c>
       <c r="D12" s="1">
-        <v>46193.56041666667</v>
+        <v>46193.31041666667</v>
       </c>
       <c r="E12">
         <v>6697</v>
@@ -4078,7 +4078,7 @@
         <v>46193.31079591435</v>
       </c>
       <c r="D13" s="1">
-        <v>46193.56076388889</v>
+        <v>46193.31076388889</v>
       </c>
       <c r="E13">
         <v>7261</v>
@@ -4200,7 +4200,7 @@
         <v>46193.311139363424</v>
       </c>
       <c r="D14" s="1">
-        <v>46193.561111111114</v>
+        <v>46193.311111111114</v>
       </c>
       <c r="E14">
         <v>7865</v>
@@ -4322,7 +4322,7 @@
         <v>46193.31148658565</v>
       </c>
       <c r="D15" s="1">
-        <v>46193.56145833333</v>
+        <v>46193.31145833333</v>
       </c>
       <c r="E15">
         <v>8462</v>
@@ -4444,7 +4444,7 @@
         <v>46193.312180532404</v>
       </c>
       <c r="D16" s="1">
-        <v>46193.56215277778</v>
+        <v>46193.31215277778</v>
       </c>
       <c r="E16">
         <v>9657</v>
@@ -4566,7 +4566,7 @@
         <v>46193.31252828704</v>
       </c>
       <c r="D17" s="1">
-        <v>46193.5625</v>
+        <v>46193.3125</v>
       </c>
       <c r="E17">
         <v>10310</v>
@@ -4688,7 +4688,7 @@
         <v>46193.31287951389</v>
       </c>
       <c r="D18" s="1">
-        <v>46193.56284722222</v>
+        <v>46193.31284722222</v>
       </c>
       <c r="E18">
         <v>10963</v>
@@ -4810,7 +4810,7 @@
         <v>46193.31322215278</v>
       </c>
       <c r="D19" s="1">
-        <v>46193.56319444445</v>
+        <v>46193.31319444445</v>
       </c>
       <c r="E19">
         <v>11603</v>
@@ -4932,7 +4932,7 @@
         <v>46193.313569907405</v>
       </c>
       <c r="D20" s="1">
-        <v>46193.56354166667</v>
+        <v>46193.31354166667</v>
       </c>
       <c r="E20">
         <v>12239</v>
@@ -5054,7 +5054,7 @@
         <v>46193.313920671295</v>
       </c>
       <c r="D21" s="1">
-        <v>46193.563888888886</v>
+        <v>46193.313888888886</v>
       </c>
       <c r="E21">
         <v>12885</v>
@@ -5176,7 +5176,7 @@
         <v>46193.31426416666</v>
       </c>
       <c r="D22" s="1">
-        <v>46193.56423611111</v>
+        <v>46193.31423611111</v>
       </c>
       <c r="E22">
         <v>13529</v>
@@ -5298,7 +5298,7 @@
         <v>46193.314611608796</v>
       </c>
       <c r="D23" s="1">
-        <v>46193.56458333333</v>
+        <v>46193.31458333333</v>
       </c>
       <c r="E23">
         <v>14129</v>
@@ -5420,7 +5420,7 @@
         <v>46193.314962881945</v>
       </c>
       <c r="D24" s="1">
-        <v>46193.564930555556</v>
+        <v>46193.314930555556</v>
       </c>
       <c r="E24">
         <v>14785</v>
@@ -5542,7 +5542,7 @@
         <v>46193.31530559028</v>
       </c>
       <c r="D25" s="1">
-        <v>46193.56527777778</v>
+        <v>46193.31527777778</v>
       </c>
       <c r="E25">
         <v>15287</v>
@@ -5664,7 +5664,7 @@
         <v>46193.31565283565</v>
       </c>
       <c r="D26" s="1">
-        <v>46193.565625</v>
+        <v>46193.315625</v>
       </c>
       <c r="E26">
         <v>15848</v>
@@ -5786,7 +5786,7 @@
         <v>46193.316004016204</v>
       </c>
       <c r="D27" s="1">
-        <v>46193.56597222222</v>
+        <v>46193.31597222222</v>
       </c>
       <c r="E27">
         <v>16492</v>
@@ -5908,7 +5908,7 @@
         <v>46193.31634773148</v>
       </c>
       <c r="D28" s="1">
-        <v>46193.56631944444</v>
+        <v>46193.31631944444</v>
       </c>
       <c r="E28">
         <v>17128</v>
@@ -6030,7 +6030,7 @@
         <v>46193.31669450231</v>
       </c>
       <c r="D29" s="1">
-        <v>46193.566666666666</v>
+        <v>46193.316666666666</v>
       </c>
       <c r="E29">
         <v>17811</v>
@@ -6152,7 +6152,7 @@
         <v>46193.31704555556</v>
       </c>
       <c r="D30" s="1">
-        <v>46193.56701388889</v>
+        <v>46193.31701388889</v>
       </c>
       <c r="E30">
         <v>18411</v>
@@ -6274,7 +6274,7 @@
         <v>46193.317389317126</v>
       </c>
       <c r="D31" s="1">
-        <v>46193.56736111111</v>
+        <v>46193.31736111111</v>
       </c>
       <c r="E31">
         <v>19031</v>
@@ -6396,7 +6396,7 @@
         <v>46193.317736412035</v>
       </c>
       <c r="D32" s="1">
-        <v>46193.567708333336</v>
+        <v>46193.317708333336</v>
       </c>
       <c r="E32">
         <v>19701</v>
@@ -6518,7 +6518,7 @@
         <v>46193.31808748843</v>
       </c>
       <c r="D33" s="1">
-        <v>46193.56805555556</v>
+        <v>46193.31805555556</v>
       </c>
       <c r="E33">
         <v>20367</v>
@@ -6640,7 +6640,7 @@
         <v>46193.31843193287</v>
       </c>
       <c r="D34" s="1">
-        <v>46193.568402777775</v>
+        <v>46193.318402777775</v>
       </c>
       <c r="E34">
         <v>20905</v>
@@ -6762,7 +6762,7 @@
         <v>46193.31877829861</v>
       </c>
       <c r="D35" s="1">
-        <v>46193.56875</v>
+        <v>46193.31875</v>
       </c>
       <c r="E35">
         <v>21578</v>
@@ -6884,7 +6884,7 @@
         <v>46193.31912923611</v>
       </c>
       <c r="D36" s="1">
-        <v>46193.56909722222</v>
+        <v>46193.31909722222</v>
       </c>
       <c r="E36">
         <v>22247</v>
@@ -7006,7 +7006,7 @@
         <v>46193.31947230324</v>
       </c>
       <c r="D37" s="1">
-        <v>46193.569444444445</v>
+        <v>46193.319444444445</v>
       </c>
       <c r="E37">
         <v>22831</v>
@@ -7128,7 +7128,7 @@
         <v>46193.31981958333</v>
       </c>
       <c r="D38" s="1">
-        <v>46193.56979166667</v>
+        <v>46193.31979166667</v>
       </c>
       <c r="E38">
         <v>23326</v>
@@ -7250,7 +7250,7 @@
         <v>46193.32017048611</v>
       </c>
       <c r="D39" s="1">
-        <v>46193.57013888889</v>
+        <v>46193.32013888889</v>
       </c>
       <c r="E39">
         <v>23996</v>
@@ -7372,7 +7372,7 @@
         <v>46193.32051454861</v>
       </c>
       <c r="D40" s="1">
-        <v>46193.57048611111</v>
+        <v>46193.32048611111</v>
       </c>
       <c r="E40">
         <v>24747</v>
@@ -7494,7 +7494,7 @@
         <v>46193.320862106484</v>
       </c>
       <c r="D41" s="1">
-        <v>46193.57083333333</v>
+        <v>46193.32083333333</v>
       </c>
       <c r="E41">
         <v>25420</v>
@@ -7616,7 +7616,7 @@
         <v>46193.32121256944</v>
       </c>
       <c r="D42" s="1">
-        <v>46193.571180555555</v>
+        <v>46193.321180555555</v>
       </c>
       <c r="E42">
         <v>26152</v>
@@ -7738,7 +7738,7 @@
         <v>46193.321556030096</v>
       </c>
       <c r="D43" s="1">
-        <v>46193.57152777778</v>
+        <v>46193.32152777778</v>
       </c>
       <c r="E43">
         <v>26768</v>
@@ -7860,7 +7860,7 @@
         <v>46193.32190329861</v>
       </c>
       <c r="D44" s="1">
-        <v>46193.571875</v>
+        <v>46193.321875</v>
       </c>
       <c r="E44">
         <v>27270</v>
@@ -7982,7 +7982,7 @@
         <v>46193.32225464121</v>
       </c>
       <c r="D45" s="1">
-        <v>46193.572222222225</v>
+        <v>46193.322222222225</v>
       </c>
       <c r="E45">
         <v>27756</v>
@@ -8104,7 +8104,7 @@
         <v>46193.32259732639</v>
       </c>
       <c r="D46" s="1">
-        <v>46193.57256944444</v>
+        <v>46193.32256944444</v>
       </c>
       <c r="E46">
         <v>28281</v>
@@ -8226,7 +8226,7 @@
         <v>46193.32294524305</v>
       </c>
       <c r="D47" s="1">
-        <v>46193.572916666664</v>
+        <v>46193.322916666664</v>
       </c>
       <c r="E47">
         <v>28928</v>
@@ -8348,7 +8348,7 @@
         <v>46193.32329568287</v>
       </c>
       <c r="D48" s="1">
-        <v>46193.57326388889</v>
+        <v>46193.32326388889</v>
       </c>
       <c r="E48">
         <v>29597</v>
@@ -8470,7 +8470,7 @@
         <v>46193.32363961806</v>
       </c>
       <c r="D49" s="1">
-        <v>46193.57361111111</v>
+        <v>46193.32361111111</v>
       </c>
       <c r="E49">
         <v>30322</v>
@@ -8592,7 +8592,7 @@
         <v>46193.32398659722</v>
       </c>
       <c r="D50" s="1">
-        <v>46193.573958333334</v>
+        <v>46193.323958333334</v>
       </c>
       <c r="E50">
         <v>30834</v>
@@ -8714,7 +8714,7 @@
         <v>46193.3243380787</v>
       </c>
       <c r="D51" s="1">
-        <v>46193.57430555556</v>
+        <v>46193.32430555556</v>
       </c>
       <c r="E51">
         <v>31398</v>
@@ -8836,7 +8836,7 @@
         <v>46193.32468103009</v>
       </c>
       <c r="D52" s="1">
-        <v>46193.57465277778</v>
+        <v>46193.32465277778</v>
       </c>
       <c r="E52">
         <v>31963</v>
@@ -8958,7 +8958,7 @@
         <v>46193.325028576386</v>
       </c>
       <c r="D53" s="1">
-        <v>46193.575</v>
+        <v>46193.325</v>
       </c>
       <c r="E53">
         <v>32593</v>
@@ -9080,7 +9080,7 @@
         <v>46193.32538028935</v>
       </c>
       <c r="D54" s="1">
-        <v>46193.57534722222</v>
+        <v>46193.32534722222</v>
       </c>
       <c r="E54">
         <v>33213</v>
@@ -9202,7 +9202,7 @@
         <v>46193.325722291665</v>
       </c>
       <c r="D55" s="1">
-        <v>46193.575694444444</v>
+        <v>46193.325694444444</v>
       </c>
       <c r="E55">
         <v>33748</v>
@@ -9324,7 +9324,7 @@
         <v>46193.32606962963</v>
       </c>
       <c r="D56" s="1">
-        <v>46193.57604166667</v>
+        <v>46193.32604166667</v>
       </c>
       <c r="E56">
         <v>34371</v>
@@ -9446,7 +9446,7 @@
         <v>46193.32642096065</v>
       </c>
       <c r="D57" s="1">
-        <v>46193.57638888889</v>
+        <v>46193.32638888889</v>
       </c>
       <c r="E57">
         <v>35021</v>
@@ -9568,7 +9568,7 @@
         <v>46193.32676409722</v>
       </c>
       <c r="D58" s="1">
-        <v>46193.576736111114</v>
+        <v>46193.326736111114</v>
       </c>
       <c r="E58">
         <v>35651</v>
@@ -9690,7 +9690,7 @@
         <v>46193.32711116898</v>
       </c>
       <c r="D59" s="1">
-        <v>46193.57708333333</v>
+        <v>46193.32708333333</v>
       </c>
       <c r="E59">
         <v>36264</v>
@@ -9812,7 +9812,7 @@
         <v>46193.32746273148</v>
       </c>
       <c r="D60" s="1">
-        <v>46193.57743055555</v>
+        <v>46193.32743055555</v>
       </c>
       <c r="E60">
         <v>36825</v>
@@ -9934,7 +9934,7 @@
         <v>46193.32850045139</v>
       </c>
       <c r="D61" s="1">
-        <v>46193.57847222222</v>
+        <v>46193.32847222222</v>
       </c>
       <c r="E61">
         <v>38686</v>
@@ -10056,7 +10056,7 @@
         <v>46193.32885133102</v>
       </c>
       <c r="D62" s="1">
-        <v>46193.57881944445</v>
+        <v>46193.32881944445</v>
       </c>
       <c r="E62">
         <v>39342</v>
@@ -10178,7 +10178,7 @@
         <v>46193.3291946875</v>
       </c>
       <c r="D63" s="1">
-        <v>46193.57916666667</v>
+        <v>46193.32916666667</v>
       </c>
       <c r="E63">
         <v>39903</v>
@@ -10300,7 +10300,7 @@
         <v>46193.32954293981</v>
       </c>
       <c r="D64" s="1">
-        <v>46193.579513888886</v>
+        <v>46193.329513888886</v>
       </c>
       <c r="E64">
         <v>40478</v>
@@ -10422,7 +10422,7 @@
         <v>46193.329893344904</v>
       </c>
       <c r="D65" s="1">
-        <v>46193.57986111111</v>
+        <v>46193.32986111111</v>
       </c>
       <c r="E65">
         <v>41075</v>
@@ -10544,7 +10544,7 @@
         <v>46193.33023667824</v>
       </c>
       <c r="D66" s="1">
-        <v>46193.58020833333</v>
+        <v>46193.33020833333</v>
       </c>
       <c r="E66">
         <v>41793</v>
@@ -10666,7 +10666,7 @@
         <v>46193.33058395833</v>
       </c>
       <c r="D67" s="1">
-        <v>46193.580555555556</v>
+        <v>46193.330555555556</v>
       </c>
       <c r="E67">
         <v>42440</v>
@@ -10788,7 +10788,7 @@
         <v>46193.33093429398</v>
       </c>
       <c r="D68" s="1">
-        <v>46193.58090277778</v>
+        <v>46193.33090277778</v>
       </c>
       <c r="E68">
         <v>43043</v>
@@ -10913,7 +10913,7 @@
         <v>46193.331277916666</v>
       </c>
       <c r="D69" s="1">
-        <v>46193.58125</v>
+        <v>46193.33125</v>
       </c>
       <c r="E69">
         <v>43582</v>
@@ -11035,7 +11035,7 @@
         <v>46193.331624907405</v>
       </c>
       <c r="D70" s="1">
-        <v>46193.58159722222</v>
+        <v>46193.33159722222</v>
       </c>
       <c r="E70">
         <v>44093</v>
@@ -11157,7 +11157,7 @@
         <v>46193.331976030095</v>
       </c>
       <c r="D71" s="1">
-        <v>46193.58194444444</v>
+        <v>46193.33194444444</v>
       </c>
       <c r="E71">
         <v>44628</v>
@@ -11279,7 +11279,7 @@
         <v>46193.332320092595</v>
       </c>
       <c r="D72" s="1">
-        <v>46193.582291666666</v>
+        <v>46193.332291666666</v>
       </c>
       <c r="E72">
         <v>45134</v>
@@ -11401,7 +11401,7 @@
         <v>46193.332667511575</v>
       </c>
       <c r="D73" s="1">
-        <v>46193.58263888889</v>
+        <v>46193.33263888889</v>
       </c>
       <c r="E73">
         <v>45655</v>
@@ -11523,7 +11523,7 @@
         <v>46193.333018136575</v>
       </c>
       <c r="D74" s="1">
-        <v>46193.58298611111</v>
+        <v>46193.33298611111</v>
       </c>
       <c r="E74">
         <v>46285</v>
@@ -11645,7 +11645,7 @@
         <v>46193.33336152778</v>
       </c>
       <c r="D75" s="1">
-        <v>46193.583333333336</v>
+        <v>46193.333333333336</v>
       </c>
       <c r="E75">
         <v>46942</v>
@@ -11767,7 +11767,7 @@
         <v>46193.33370912037</v>
       </c>
       <c r="D76" s="1">
-        <v>46193.58368055556</v>
+        <v>46193.33368055556</v>
       </c>
       <c r="E76">
         <v>47408</v>
@@ -11889,7 +11889,7 @@
         <v>46193.33405980324</v>
       </c>
       <c r="D77" s="1">
-        <v>46193.584027777775</v>
+        <v>46193.334027777775</v>
       </c>
       <c r="E77">
         <v>47903</v>
@@ -12011,7 +12011,7 @@
         <v>46193.33440310185</v>
       </c>
       <c r="D78" s="1">
-        <v>46193.584375</v>
+        <v>46193.334375</v>
       </c>
       <c r="E78">
         <v>48425</v>
@@ -12133,7 +12133,7 @@
         <v>46193.33475099537</v>
       </c>
       <c r="D79" s="1">
-        <v>46193.58472222222</v>
+        <v>46193.33472222222</v>
       </c>
       <c r="E79">
         <v>48914</v>
@@ -12255,7 +12255,7 @@
         <v>46193.3351015625</v>
       </c>
       <c r="D80" s="1">
-        <v>46193.585069444445</v>
+        <v>46193.335069444445</v>
       </c>
       <c r="E80">
         <v>49403</v>
@@ -12377,7 +12377,7 @@
         <v>46193.335444675926</v>
       </c>
       <c r="D81" s="1">
-        <v>46193.58541666667</v>
+        <v>46193.33541666667</v>
       </c>
       <c r="E81">
         <v>49898</v>
@@ -12499,7 +12499,7 @@
         <v>46193.33579197917</v>
       </c>
       <c r="D82" s="1">
-        <v>46193.58576388889</v>
+        <v>46193.33576388889</v>
       </c>
       <c r="E82">
         <v>50403</v>
@@ -12621,7 +12621,7 @@
         <v>46193.336487025466</v>
       </c>
       <c r="D83" s="1">
-        <v>46193.58645833333</v>
+        <v>46193.33645833333</v>
       </c>
       <c r="E83">
         <v>51427</v>
@@ -12743,7 +12743,7 @@
         <v>46193.33683366898</v>
       </c>
       <c r="D84" s="1">
-        <v>46193.586805555555</v>
+        <v>46193.336805555555</v>
       </c>
       <c r="E84">
         <v>51959</v>
@@ -12865,7 +12865,7 @@
         <v>46193.33718458333</v>
       </c>
       <c r="D85" s="1">
-        <v>46193.58715277778</v>
+        <v>46193.33715277778</v>
       </c>
       <c r="E85">
         <v>52526</v>
@@ -12987,7 +12987,7 @@
         <v>46193.33752784722</v>
       </c>
       <c r="D86" s="1">
-        <v>46193.5875</v>
+        <v>46193.3375</v>
       </c>
       <c r="E86">
         <v>53078</v>
@@ -13109,7 +13109,7 @@
         <v>46193.3378752662</v>
       </c>
       <c r="D87" s="1">
-        <v>46193.587847222225</v>
+        <v>46193.337847222225</v>
       </c>
       <c r="E87">
         <v>53701</v>
@@ -13231,7 +13231,7 @@
         <v>46193.33822648148</v>
       </c>
       <c r="D88" s="1">
-        <v>46193.58819444444</v>
+        <v>46193.33819444444</v>
       </c>
       <c r="E88">
         <v>54259</v>
@@ -13353,7 +13353,7 @@
         <v>46193.338569618056</v>
       </c>
       <c r="D89" s="1">
-        <v>46193.588541666664</v>
+        <v>46193.338541666664</v>
       </c>
       <c r="E89">
         <v>54800</v>
@@ -13475,7 +13475,7 @@
         <v>46193.338917256944</v>
       </c>
       <c r="D90" s="1">
-        <v>46193.58888888889</v>
+        <v>46193.33888888889</v>
       </c>
       <c r="E90">
         <v>55345</v>
@@ -13597,7 +13597,7 @@
         <v>46193.342390046295</v>
       </c>
       <c r="D91" s="1">
-        <v>46193.592361111114</v>
+        <v>46193.342361111114</v>
       </c>
       <c r="E91">
         <v>60995</v>
@@ -13719,7 +13719,7 @@
         <v>46193.34274030093</v>
       </c>
       <c r="D92" s="1">
-        <v>46193.59270833333</v>
+        <v>46193.34270833333</v>
       </c>
       <c r="E92">
         <v>61563</v>
@@ -13841,7 +13841,7 @@
         <v>46193.34308431713</v>
       </c>
       <c r="D93" s="1">
-        <v>46193.59305555555</v>
+        <v>46193.34305555555</v>
       </c>
       <c r="E93">
         <v>62081</v>
@@ -13963,7 +13963,7 @@
         <v>46193.34343129629</v>
       </c>
       <c r="D94" s="1">
-        <v>46193.59340277778</v>
+        <v>46193.34340277778</v>
       </c>
       <c r="E94">
         <v>62639</v>
@@ -14085,7 +14085,7 @@
         <v>46193.34378263889</v>
       </c>
       <c r="D95" s="1">
-        <v>46193.59375</v>
+        <v>46193.34375</v>
       </c>
       <c r="E95">
         <v>63161</v>
@@ -14207,7 +14207,7 @@
         <v>46193.34412512732</v>
       </c>
       <c r="D96" s="1">
-        <v>46193.59409722222</v>
+        <v>46193.34409722222</v>
       </c>
       <c r="E96">
         <v>63715</v>
@@ -14329,7 +14329,7 @@
         <v>46193.34447269676</v>
       </c>
       <c r="D97" s="1">
-        <v>46193.59444444445</v>
+        <v>46193.34444444445</v>
       </c>
       <c r="E97">
         <v>64273</v>
@@ -14451,7 +14451,7 @@
         <v>46193.344824085645</v>
       </c>
       <c r="D98" s="1">
-        <v>46193.59479166667</v>
+        <v>46193.34479166667</v>
       </c>
       <c r="E98">
         <v>64811</v>
@@ -14573,7 +14573,7 @@
         <v>46193.34516783565</v>
       </c>
       <c r="D99" s="1">
-        <v>46193.595138888886</v>
+        <v>46193.345138888886</v>
       </c>
       <c r="E99">
         <v>65366</v>
@@ -14695,7 +14695,7 @@
         <v>46193.345515023146</v>
       </c>
       <c r="D100" s="1">
-        <v>46193.59548611111</v>
+        <v>46193.34548611111</v>
       </c>
       <c r="E100">
         <v>65943</v>
@@ -14817,7 +14817,7 @@
         <v>46193.34586592593</v>
       </c>
       <c r="D101" s="1">
-        <v>46193.59583333333</v>
+        <v>46193.34583333333</v>
       </c>
       <c r="E101">
         <v>66531</v>
@@ -14939,7 +14939,7 @@
         <v>46193.34620862269</v>
       </c>
       <c r="D102" s="1">
-        <v>46193.596180555556</v>
+        <v>46193.346180555556</v>
       </c>
       <c r="E102">
         <v>67059</v>
@@ -15061,7 +15061,7 @@
         <v>46193.34690370371</v>
       </c>
       <c r="D103" s="1">
-        <v>46193.596875</v>
+        <v>46193.346875</v>
       </c>
       <c r="E103">
         <v>68158</v>
@@ -15183,7 +15183,7 @@
         <v>46193.34725368056</v>
       </c>
       <c r="D104" s="1">
-        <v>46193.59722222222</v>
+        <v>46193.34722222222</v>
       </c>
       <c r="E104">
         <v>68719</v>
@@ -15305,7 +15305,7 @@
         <v>46193.34759839121</v>
       </c>
       <c r="D105" s="1">
-        <v>46193.59756944444</v>
+        <v>46193.34756944444</v>
       </c>
       <c r="E105">
         <v>69287</v>
@@ -15427,7 +15427,7 @@
         <v>46193.34794535879</v>
       </c>
       <c r="D106" s="1">
-        <v>46193.597916666666</v>
+        <v>46193.347916666666</v>
       </c>
       <c r="E106">
         <v>69841</v>
@@ -15549,7 +15549,7 @@
         <v>46193.348296412034</v>
       </c>
       <c r="D107" s="1">
-        <v>46193.59826388889</v>
+        <v>46193.34826388889</v>
       </c>
       <c r="E107">
         <v>70396</v>
@@ -15671,7 +15671,7 @@
         <v>46193.34863927084</v>
       </c>
       <c r="D108" s="1">
-        <v>46193.59861111111</v>
+        <v>46193.34861111111</v>
       </c>
       <c r="E108">
         <v>70973</v>
@@ -15796,7 +15796,7 @@
         <v>46193.34898664352</v>
       </c>
       <c r="D109" s="1">
-        <v>46193.598958333336</v>
+        <v>46193.348958333336</v>
       </c>
       <c r="E109">
         <v>71567</v>
@@ -15918,7 +15918,7 @@
         <v>46193.349337569445</v>
       </c>
       <c r="D110" s="1">
-        <v>46193.59930555556</v>
+        <v>46193.34930555556</v>
       </c>
       <c r="E110">
         <v>72174</v>
@@ -16040,7 +16040,7 @@
         <v>46193.35002767361</v>
       </c>
       <c r="D111" s="1">
-        <v>46193.6</v>
+        <v>46193.35</v>
       </c>
       <c r="E111">
         <v>73382</v>
@@ -16162,7 +16162,7 @@
         <v>46193.35037949074</v>
       </c>
       <c r="D112" s="1">
-        <v>46193.60034722222</v>
+        <v>46193.35034722222</v>
       </c>
       <c r="E112">
         <v>74002</v>
@@ -16284,7 +16284,7 @@
         <v>46193.350723055555</v>
       </c>
       <c r="D113" s="1">
-        <v>46193.600694444445</v>
+        <v>46193.350694444445</v>
       </c>
       <c r="E113">
         <v>74583</v>
@@ -16406,7 +16406,7 @@
         <v>46193.35142146991</v>
       </c>
       <c r="D114" s="1">
-        <v>46193.60138888889</v>
+        <v>46193.35138888889</v>
       </c>
       <c r="E114">
         <v>75761</v>
@@ -16528,7 +16528,7 @@
         <v>46193.351765</v>
       </c>
       <c r="D115" s="1">
-        <v>46193.60173611111</v>
+        <v>46193.35173611111</v>
       </c>
       <c r="E115">
         <v>76371</v>
@@ -16650,7 +16650,7 @@
         <v>46193.352111493055</v>
       </c>
       <c r="D116" s="1">
-        <v>46193.60208333333</v>
+        <v>46193.35208333333</v>
       </c>
       <c r="E116">
         <v>77014</v>
@@ -16772,7 +16772,7 @@
         <v>46193.35246255787</v>
       </c>
       <c r="D117" s="1">
-        <v>46193.602430555555</v>
+        <v>46193.352430555555</v>
       </c>
       <c r="E117">
         <v>77638</v>
@@ -16894,7 +16894,7 @@
         <v>46193.35280648148</v>
       </c>
       <c r="D118" s="1">
-        <v>46193.60277777778</v>
+        <v>46193.35277777778</v>
       </c>
       <c r="E118">
         <v>78258</v>
@@ -17016,7 +17016,7 @@
         <v>46193.353153634256</v>
       </c>
       <c r="D119" s="1">
-        <v>46193.603125</v>
+        <v>46193.353125</v>
       </c>
       <c r="E119">
         <v>78881</v>
@@ -17138,7 +17138,7 @@
         <v>46193.35350469907</v>
       </c>
       <c r="D120" s="1">
-        <v>46193.603472222225</v>
+        <v>46193.353472222225</v>
       </c>
       <c r="E120">
         <v>79492</v>
@@ -17260,7 +17260,7 @@
         <v>46193.353847604165</v>
       </c>
       <c r="D121" s="1">
-        <v>46193.60381944444</v>
+        <v>46193.35381944444</v>
       </c>
       <c r="E121">
         <v>80154</v>
@@ -17382,7 +17382,7 @@
         <v>46193.354196168984</v>
       </c>
       <c r="D122" s="1">
-        <v>46193.604166666664</v>
+        <v>46193.354166666664</v>
       </c>
       <c r="E122">
         <v>80791</v>
@@ -17504,7 +17504,7 @@
         <v>46193.354545925926</v>
       </c>
       <c r="D123" s="1">
-        <v>46193.60451388889</v>
+        <v>46193.35451388889</v>
       </c>
       <c r="E123">
         <v>81405</v>
@@ -17626,7 +17626,7 @@
         <v>46193.35488951389</v>
       </c>
       <c r="D124" s="1">
-        <v>46193.60486111111</v>
+        <v>46193.35486111111</v>
       </c>
       <c r="E124">
         <v>82025</v>
@@ -17748,7 +17748,7 @@
         <v>46193.35523799768</v>
       </c>
       <c r="D125" s="1">
-        <v>46193.605208333334</v>
+        <v>46193.355208333334</v>
       </c>
       <c r="E125">
         <v>82632</v>
@@ -17870,7 +17870,7 @@
         <v>46193.35558782407</v>
       </c>
       <c r="D126" s="1">
-        <v>46193.60555555556</v>
+        <v>46193.35555555556</v>
       </c>
       <c r="E126">
         <v>83275</v>
@@ -17992,7 +17992,7 @@
         <v>46193.35593144676</v>
       </c>
       <c r="D127" s="1">
-        <v>46193.60590277778</v>
+        <v>46193.35590277778</v>
       </c>
       <c r="E127">
         <v>83885</v>
@@ -18114,7 +18114,7 @@
         <v>46193.356278391206</v>
       </c>
       <c r="D128" s="1">
-        <v>46193.60625</v>
+        <v>46193.35625</v>
       </c>
       <c r="E128">
         <v>84535</v>
@@ -18236,7 +18236,7 @@
         <v>46193.35662880787</v>
       </c>
       <c r="D129" s="1">
-        <v>46193.60659722222</v>
+        <v>46193.35659722222</v>
       </c>
       <c r="E129">
         <v>85188</v>
@@ -18358,7 +18358,7 @@
         <v>46193.35732145833</v>
       </c>
       <c r="D130" s="1">
-        <v>46193.60729166667</v>
+        <v>46193.35729166667</v>
       </c>
       <c r="E130">
         <v>86425</v>
@@ -18480,7 +18480,7 @@
         <v>46193.35801755787</v>
       </c>
       <c r="D131" s="1">
-        <v>46193.607986111114</v>
+        <v>46193.357986111114</v>
       </c>
       <c r="E131">
         <v>87616</v>
@@ -18602,7 +18602,7 @@
         <v>46193.35905591435</v>
       </c>
       <c r="D132" s="1">
-        <v>46193.60902777778</v>
+        <v>46193.35902777778</v>
       </c>
       <c r="E132">
         <v>89526</v>
@@ -18724,7 +18724,7 @@
         <v>46193.3594037963</v>
       </c>
       <c r="D133" s="1">
-        <v>46193.609375</v>
+        <v>46193.359375</v>
       </c>
       <c r="E133">
         <v>90165</v>
@@ -18846,7 +18846,7 @@
         <v>46193.35975398148</v>
       </c>
       <c r="D134" s="1">
-        <v>46193.60972222222</v>
+        <v>46193.35972222222</v>
       </c>
       <c r="E134">
         <v>90809</v>
@@ -18968,7 +18968,7 @@
         <v>46193.36009741898</v>
       </c>
       <c r="D135" s="1">
-        <v>46193.61006944445</v>
+        <v>46193.36006944445</v>
       </c>
       <c r="E135">
         <v>91462</v>
@@ -19090,7 +19090,7 @@
         <v>46193.36079331019</v>
       </c>
       <c r="D136" s="1">
-        <v>46193.610763888886</v>
+        <v>46193.360763888886</v>
       </c>
       <c r="E136">
         <v>92653</v>
@@ -19212,7 +19212,7 @@
         <v>46193.36114284722</v>
       </c>
       <c r="D137" s="1">
-        <v>46193.61111111111</v>
+        <v>46193.36111111111</v>
       </c>
       <c r="E137">
         <v>93201</v>
@@ -19334,7 +19334,7 @@
         <v>46193.36183364583</v>
       </c>
       <c r="D138" s="1">
-        <v>46193.611805555556</v>
+        <v>46193.361805555556</v>
       </c>
       <c r="E138">
         <v>94365</v>
@@ -19456,7 +19456,7 @@
         <v>46193.362181261575</v>
       </c>
       <c r="D139" s="1">
-        <v>46193.61215277778</v>
+        <v>46193.36215277778</v>
       </c>
       <c r="E139">
         <v>95005</v>
@@ -19578,7 +19578,7 @@
         <v>46193.363223125</v>
       </c>
       <c r="D140" s="1">
-        <v>46193.61319444444</v>
+        <v>46193.36319444444</v>
       </c>
       <c r="E140">
         <v>96990</v>
@@ -19700,7 +19700,7 @@
         <v>46193.36426465278</v>
       </c>
       <c r="D141" s="1">
-        <v>46193.61423611111</v>
+        <v>46193.36423611111</v>
       </c>
       <c r="E141">
         <v>98772</v>
@@ -19822,7 +19822,7 @@
         <v>46193.364958796294</v>
       </c>
       <c r="D142" s="1">
-        <v>46193.61493055556</v>
+        <v>46193.36493055556</v>
       </c>
       <c r="E142">
         <v>99858</v>
@@ -19944,7 +19944,7 @@
         <v>46193.36530618055</v>
       </c>
       <c r="D143" s="1">
-        <v>46193.615277777775</v>
+        <v>46193.365277777775</v>
       </c>
       <c r="E143">
         <v>100442</v>
@@ -20222,7 +20222,7 @@
         <v>46193.36600140046</v>
       </c>
       <c r="D2" s="1">
-        <v>46193.61597222222</v>
+        <v>46193.36597222222</v>
       </c>
       <c r="E2">
         <v>100065</v>
@@ -20308,7 +20308,7 @@
         <v>46193.36634741898</v>
       </c>
       <c r="D3" s="1">
-        <v>46193.616319444445</v>
+        <v>46193.366319444445</v>
       </c>
       <c r="E3">
         <v>96853</v>
@@ -20418,7 +20418,7 @@
         <v>46193.36669859954</v>
       </c>
       <c r="D4" s="1">
-        <v>46193.61666666667</v>
+        <v>46193.36666666667</v>
       </c>
       <c r="E4">
         <v>93906</v>
@@ -20540,7 +20540,7 @@
         <v>46193.36704149305</v>
       </c>
       <c r="D5" s="1">
-        <v>46193.61701388889</v>
+        <v>46193.36701388889</v>
       </c>
       <c r="E5">
         <v>91009</v>
@@ -20662,7 +20662,7 @@
         <v>46193.3673896875</v>
       </c>
       <c r="D6" s="1">
-        <v>46193.61736111111</v>
+        <v>46193.36736111111</v>
       </c>
       <c r="E6">
         <v>88321</v>
@@ -20784,7 +20784,7 @@
         <v>46193.367739733796</v>
       </c>
       <c r="D7" s="1">
-        <v>46193.61770833333</v>
+        <v>46193.36770833333</v>
       </c>
       <c r="E7">
         <v>85811</v>
@@ -20906,7 +20906,7 @@
         <v>46193.36808447917</v>
       </c>
       <c r="D8" s="1">
-        <v>46193.618055555555</v>
+        <v>46193.368055555555</v>
       </c>
       <c r="E8">
         <v>83498</v>
@@ -21028,7 +21028,7 @@
         <v>46193.3684309838</v>
       </c>
       <c r="D9" s="1">
-        <v>46193.61840277778</v>
+        <v>46193.36840277778</v>
       </c>
       <c r="E9">
         <v>81355</v>
@@ -21150,7 +21150,7 @@
         <v>46193.369125578705</v>
       </c>
       <c r="D10" s="1">
-        <v>46193.619097222225</v>
+        <v>46193.369097222225</v>
       </c>
       <c r="E10">
         <v>77431</v>
@@ -21272,7 +21272,7 @@
         <v>46193.36947380787</v>
       </c>
       <c r="D11" s="1">
-        <v>46193.61944444444</v>
+        <v>46193.36944444444</v>
       </c>
       <c r="E11">
         <v>75580</v>
@@ -21394,7 +21394,7 @@
         <v>46193.369823726855</v>
       </c>
       <c r="D12" s="1">
-        <v>46193.619791666664</v>
+        <v>46193.369791666664</v>
       </c>
       <c r="E12">
         <v>73812</v>
@@ -21516,7 +21516,7 @@
         <v>46193.3701672338</v>
       </c>
       <c r="D13" s="1">
-        <v>46193.62013888889</v>
+        <v>46193.37013888889</v>
       </c>
       <c r="E13">
         <v>72145</v>
@@ -21638,7 +21638,7 @@
         <v>46193.37051392361</v>
       </c>
       <c r="D14" s="1">
-        <v>46193.62048611111</v>
+        <v>46193.37048611111</v>
       </c>
       <c r="E14">
         <v>70521</v>
@@ -21760,7 +21760,7 @@
         <v>46193.3712090162</v>
       </c>
       <c r="D15" s="1">
-        <v>46193.62118055556</v>
+        <v>46193.37118055556</v>
       </c>
       <c r="E15">
         <v>67394</v>
@@ -21882,7 +21882,7 @@
         <v>46193.37155581018</v>
       </c>
       <c r="D16" s="1">
-        <v>46193.62152777778</v>
+        <v>46193.37152777778</v>
       </c>
       <c r="E16">
         <v>65930</v>
@@ -22004,7 +22004,7 @@
         <v>46193.371906782406</v>
       </c>
       <c r="D17" s="1">
-        <v>46193.621875</v>
+        <v>46193.371875</v>
       </c>
       <c r="E17">
         <v>64647</v>
@@ -22126,7 +22126,7 @@
         <v>46193.37225018519</v>
       </c>
       <c r="D18" s="1">
-        <v>46193.62222222222</v>
+        <v>46193.37222222222</v>
       </c>
       <c r="E18">
         <v>63348</v>
@@ -22248,7 +22248,7 @@
         <v>46193.37259917824</v>
       </c>
       <c r="D19" s="1">
-        <v>46193.622569444444</v>
+        <v>46193.372569444444</v>
       </c>
       <c r="E19">
         <v>62094</v>
@@ -22370,7 +22370,7 @@
         <v>46193.37294854167</v>
       </c>
       <c r="D20" s="1">
-        <v>46193.62291666667</v>
+        <v>46193.37291666667</v>
       </c>
       <c r="E20">
         <v>60893</v>
@@ -22492,7 +22492,7 @@
         <v>46193.37329186343</v>
       </c>
       <c r="D21" s="1">
-        <v>46193.62326388889</v>
+        <v>46193.37326388889</v>
       </c>
       <c r="E21">
         <v>59817</v>
@@ -22614,7 +22614,7 @@
         <v>46193.373639398145</v>
       </c>
       <c r="D22" s="1">
-        <v>46193.623611111114</v>
+        <v>46193.373611111114</v>
       </c>
       <c r="E22">
         <v>58813</v>
@@ -22736,7 +22736,7 @@
         <v>46193.373990486114</v>
       </c>
       <c r="D23" s="1">
-        <v>46193.62395833333</v>
+        <v>46193.37395833333</v>
       </c>
       <c r="E23">
         <v>57806</v>
@@ -22858,7 +22858,7 @@
         <v>46193.374334155094</v>
       </c>
       <c r="D24" s="1">
-        <v>46193.62430555555</v>
+        <v>46193.37430555555</v>
       </c>
       <c r="E24">
         <v>56838</v>
@@ -22980,7 +22980,7 @@
         <v>46193.37468181713</v>
       </c>
       <c r="D25" s="1">
-        <v>46193.62465277778</v>
+        <v>46193.37465277778</v>
       </c>
       <c r="E25">
         <v>55922</v>
@@ -23102,7 +23102,7 @@
         <v>46193.375031875</v>
       </c>
       <c r="D26" s="1">
-        <v>46193.625</v>
+        <v>46193.375</v>
       </c>
       <c r="E26">
         <v>55017</v>
@@ -23224,7 +23224,7 @@
         <v>46193.37537537037</v>
       </c>
       <c r="D27" s="1">
-        <v>46193.62534722222</v>
+        <v>46193.37534722222</v>
       </c>
       <c r="E27">
         <v>54124</v>
@@ -23346,7 +23346,7 @@
         <v>46193.37572293982</v>
       </c>
       <c r="D28" s="1">
-        <v>46193.62569444445</v>
+        <v>46193.37569444445</v>
       </c>
       <c r="E28">
         <v>53238</v>
@@ -23468,7 +23468,7 @@
         <v>46193.37607362268</v>
       </c>
       <c r="D29" s="1">
-        <v>46193.62604166667</v>
+        <v>46193.37604166667</v>
       </c>
       <c r="E29">
         <v>52352</v>
@@ -23590,7 +23590,7 @@
         <v>46193.37641732639</v>
       </c>
       <c r="D30" s="1">
-        <v>46193.626388888886</v>
+        <v>46193.376388888886</v>
       </c>
       <c r="E30">
         <v>51506</v>
@@ -23712,7 +23712,7 @@
         <v>46193.37676454861</v>
       </c>
       <c r="D31" s="1">
-        <v>46193.62673611111</v>
+        <v>46193.37673611111</v>
       </c>
       <c r="E31">
         <v>50705</v>
@@ -23834,7 +23834,7 @@
         <v>46193.377115752315</v>
       </c>
       <c r="D32" s="1">
-        <v>46193.62708333333</v>
+        <v>46193.37708333333</v>
       </c>
       <c r="E32">
         <v>49914</v>
@@ -23956,7 +23956,7 @@
         <v>46193.37745896991</v>
       </c>
       <c r="D33" s="1">
-        <v>46193.627430555556</v>
+        <v>46193.377430555556</v>
       </c>
       <c r="E33">
         <v>49140</v>
@@ -24078,7 +24078,7 @@
         <v>46193.37780594907</v>
       </c>
       <c r="D34" s="1">
-        <v>46193.62777777778</v>
+        <v>46193.37777777778</v>
       </c>
       <c r="E34">
         <v>48389</v>
@@ -24200,7 +24200,7 @@
         <v>46193.37815707176</v>
       </c>
       <c r="D35" s="1">
-        <v>46193.628125</v>
+        <v>46193.378125</v>
       </c>
       <c r="E35">
         <v>47634</v>
@@ -24322,7 +24322,7 @@
         <v>46193.37850082176</v>
       </c>
       <c r="D36" s="1">
-        <v>46193.62847222222</v>
+        <v>46193.37847222222</v>
       </c>
       <c r="E36">
         <v>46892</v>
@@ -24444,7 +24444,7 @@
         <v>46193.378847430555</v>
       </c>
       <c r="D37" s="1">
-        <v>46193.62881944444</v>
+        <v>46193.37881944444</v>
       </c>
       <c r="E37">
         <v>46141</v>
@@ -24566,7 +24566,7 @@
         <v>46193.37919840278</v>
       </c>
       <c r="D38" s="1">
-        <v>46193.629166666666</v>
+        <v>46193.379166666666</v>
       </c>
       <c r="E38">
         <v>45399</v>
@@ -24688,7 +24688,7 @@
         <v>46193.37954223379</v>
       </c>
       <c r="D39" s="1">
-        <v>46193.62951388889</v>
+        <v>46193.37951388889</v>
       </c>
       <c r="E39">
         <v>44687</v>
@@ -24810,7 +24810,7 @@
         <v>46193.379889375</v>
       </c>
       <c r="D40" s="1">
-        <v>46193.62986111111</v>
+        <v>46193.37986111111</v>
       </c>
       <c r="E40">
         <v>43998</v>
@@ -24932,7 +24932,7 @@
         <v>46193.38024005787</v>
       </c>
       <c r="D41" s="1">
-        <v>46193.630208333336</v>
+        <v>46193.380208333336</v>
       </c>
       <c r="E41">
         <v>43319</v>
@@ -25054,7 +25054,7 @@
         <v>46193.380584328705</v>
       </c>
       <c r="D42" s="1">
-        <v>46193.63055555556</v>
+        <v>46193.38055555556</v>
       </c>
       <c r="E42">
         <v>42637</v>
@@ -25176,7 +25176,7 @@
         <v>46193.38093068287</v>
       </c>
       <c r="D43" s="1">
-        <v>46193.630902777775</v>
+        <v>46193.380902777775</v>
       </c>
       <c r="E43">
         <v>41961</v>
@@ -25298,7 +25298,7 @@
         <v>46193.381282083334</v>
       </c>
       <c r="D44" s="1">
-        <v>46193.63125</v>
+        <v>46193.38125</v>
       </c>
       <c r="E44">
         <v>41301</v>
@@ -25420,7 +25420,7 @@
         <v>46193.38162543981</v>
       </c>
       <c r="D45" s="1">
-        <v>46193.63159722222</v>
+        <v>46193.38159722222</v>
       </c>
       <c r="E45">
         <v>40645</v>
@@ -25542,7 +25542,7 @@
         <v>46193.38197311343</v>
       </c>
       <c r="D46" s="1">
-        <v>46193.631944444445</v>
+        <v>46193.381944444445</v>
       </c>
       <c r="E46">
         <v>40008</v>
@@ -25664,7 +25664,7 @@
         <v>46193.38232362268</v>
       </c>
       <c r="D47" s="1">
-        <v>46193.63229166667</v>
+        <v>46193.38229166667</v>
       </c>
       <c r="E47">
         <v>39378</v>
@@ -25786,7 +25786,7 @@
         <v>46193.382666840276</v>
       </c>
       <c r="D48" s="1">
-        <v>46193.63263888889</v>
+        <v>46193.38263888889</v>
       </c>
       <c r="E48">
         <v>38752</v>
@@ -25908,7 +25908,7 @@
         <v>46193.38301412037</v>
       </c>
       <c r="D49" s="1">
-        <v>46193.63298611111</v>
+        <v>46193.38298611111</v>
       </c>
       <c r="E49">
         <v>38135</v>
@@ -26030,7 +26030,7 @@
         <v>46193.38336521991</v>
       </c>
       <c r="D50" s="1">
-        <v>46193.63333333333</v>
+        <v>46193.38333333333</v>
       </c>
       <c r="E50">
         <v>37528</v>
@@ -26152,7 +26152,7 @@
         <v>46193.383709155096</v>
       </c>
       <c r="D51" s="1">
-        <v>46193.633680555555</v>
+        <v>46193.383680555555</v>
       </c>
       <c r="E51">
         <v>36930</v>
@@ -26274,7 +26274,7 @@
         <v>46193.384056215276</v>
       </c>
       <c r="D52" s="1">
-        <v>46193.63402777778</v>
+        <v>46193.38402777778</v>
       </c>
       <c r="E52">
         <v>36340</v>
@@ -26396,7 +26396,7 @@
         <v>46193.384407233796</v>
       </c>
       <c r="D53" s="1">
-        <v>46193.634375</v>
+        <v>46193.384375</v>
       </c>
       <c r="E53">
         <v>35746</v>
@@ -26518,7 +26518,7 @@
         <v>46193.38475060185</v>
       </c>
       <c r="D54" s="1">
-        <v>46193.634722222225</v>
+        <v>46193.384722222225</v>
       </c>
       <c r="E54">
         <v>35165</v>
@@ -26640,7 +26640,7 @@
         <v>46193.38509775463</v>
       </c>
       <c r="D55" s="1">
-        <v>46193.63506944444</v>
+        <v>46193.38506944444</v>
       </c>
       <c r="E55">
         <v>34607</v>
@@ -26762,7 +26762,7 @@
         <v>46193.38544854167</v>
       </c>
       <c r="D56" s="1">
-        <v>46193.635416666664</v>
+        <v>46193.385416666664</v>
       </c>
       <c r="E56">
         <v>34040</v>
@@ -26884,7 +26884,7 @@
         <v>46193.385792534726</v>
       </c>
       <c r="D57" s="1">
-        <v>46193.63576388889</v>
+        <v>46193.38576388889</v>
       </c>
       <c r="E57">
         <v>33482</v>
@@ -27006,7 +27006,7 @@
         <v>46193.38613957176</v>
       </c>
       <c r="D58" s="1">
-        <v>46193.63611111111</v>
+        <v>46193.38611111111</v>
       </c>
       <c r="E58">
         <v>32918</v>
@@ -27128,7 +27128,7 @@
         <v>46193.38649024306</v>
       </c>
       <c r="D59" s="1">
-        <v>46193.636458333334</v>
+        <v>46193.386458333334</v>
       </c>
       <c r="E59">
         <v>32376</v>
@@ -27250,7 +27250,7 @@
         <v>46193.38683417824</v>
       </c>
       <c r="D60" s="1">
-        <v>46193.63680555556</v>
+        <v>46193.38680555556</v>
       </c>
       <c r="E60">
         <v>31845</v>
@@ -27372,7 +27372,7 @@
         <v>46193.38718078704</v>
       </c>
       <c r="D61" s="1">
-        <v>46193.63715277778</v>
+        <v>46193.38715277778</v>
       </c>
       <c r="E61">
         <v>31310</v>
@@ -27494,7 +27494,7 @@
         <v>46193.38753201389</v>
       </c>
       <c r="D62" s="1">
-        <v>46193.6375</v>
+        <v>46193.3875</v>
       </c>
       <c r="E62">
         <v>30791</v>
@@ -27616,7 +27616,7 @@
         <v>46193.387875706016</v>
       </c>
       <c r="D63" s="1">
-        <v>46193.63784722222</v>
+        <v>46193.38784722222</v>
       </c>
       <c r="E63">
         <v>30289</v>
@@ -27738,7 +27738,7 @@
         <v>46193.38822234954</v>
       </c>
       <c r="D64" s="1">
-        <v>46193.638194444444</v>
+        <v>46193.388194444444</v>
       </c>
       <c r="E64">
         <v>29800</v>
@@ -27860,7 +27860,7 @@
         <v>46193.38857405093</v>
       </c>
       <c r="D65" s="1">
-        <v>46193.63854166667</v>
+        <v>46193.38854166667</v>
       </c>
       <c r="E65">
         <v>29308</v>
@@ -27982,7 +27982,7 @@
         <v>46193.388916875</v>
       </c>
       <c r="D66" s="1">
-        <v>46193.63888888889</v>
+        <v>46193.38888888889</v>
       </c>
       <c r="E66">
         <v>28826</v>
@@ -28104,7 +28104,7 @@
         <v>46193.38926416667</v>
       </c>
       <c r="D67" s="1">
-        <v>46193.639236111114</v>
+        <v>46193.389236111114</v>
       </c>
       <c r="E67">
         <v>28350</v>
@@ -28226,7 +28226,7 @@
         <v>46193.38961582176</v>
       </c>
       <c r="D68" s="1">
-        <v>46193.63958333333</v>
+        <v>46193.38958333333</v>
       </c>
       <c r="E68">
         <v>27881</v>
@@ -28348,7 +28348,7 @@
         <v>46193.38995917824</v>
       </c>
       <c r="D69" s="1">
-        <v>46193.63993055555</v>
+        <v>46193.38993055555</v>
       </c>
       <c r="E69">
         <v>27412</v>
@@ -28470,7 +28470,7 @@
         <v>46193.39030648148</v>
       </c>
       <c r="D70" s="1">
-        <v>46193.64027777778</v>
+        <v>46193.39027777778</v>
       </c>
       <c r="E70">
         <v>26939</v>
@@ -28592,7 +28592,7 @@
         <v>46193.39065631945</v>
       </c>
       <c r="D71" s="1">
-        <v>46193.640625</v>
+        <v>46193.390625</v>
       </c>
       <c r="E71">
         <v>26463</v>
@@ -28714,7 +28714,7 @@
         <v>46193.39100048611</v>
       </c>
       <c r="D72" s="1">
-        <v>46193.64097222222</v>
+        <v>46193.39097222222</v>
       </c>
       <c r="E72">
         <v>25997</v>
@@ -28836,7 +28836,7 @@
         <v>46193.39134740741</v>
       </c>
       <c r="D73" s="1">
-        <v>46193.64131944445</v>
+        <v>46193.39131944445</v>
       </c>
       <c r="E73">
         <v>25525</v>
@@ -28958,7 +28958,7 @@
         <v>46193.39169878472</v>
       </c>
       <c r="D74" s="1">
-        <v>46193.64166666667</v>
+        <v>46193.39166666667</v>
       </c>
       <c r="E74">
         <v>25046</v>
@@ -29080,7 +29080,7 @@
         <v>46193.392042465275</v>
       </c>
       <c r="D75" s="1">
-        <v>46193.642013888886</v>
+        <v>46193.392013888886</v>
       </c>
       <c r="E75">
         <v>24563</v>
@@ -29202,7 +29202,7 @@
         <v>46193.3923896875</v>
       </c>
       <c r="D76" s="1">
-        <v>46193.64236111111</v>
+        <v>46193.39236111111</v>
       </c>
       <c r="E76">
         <v>24088</v>
@@ -29324,7 +29324,7 @@
         <v>46193.392740219904</v>
       </c>
       <c r="D77" s="1">
-        <v>46193.64270833333</v>
+        <v>46193.39270833333</v>
       </c>
       <c r="E77">
         <v>23605</v>
@@ -29446,7 +29446,7 @@
         <v>46193.39308386574</v>
       </c>
       <c r="D78" s="1">
-        <v>46193.643055555556</v>
+        <v>46193.393055555556</v>
       </c>
       <c r="E78">
         <v>23120</v>
@@ -29568,7 +29568,7 @@
         <v>46193.393431412034</v>
       </c>
       <c r="D79" s="1">
-        <v>46193.64340277778</v>
+        <v>46193.39340277778</v>
       </c>
       <c r="E79">
         <v>22624</v>
@@ -29690,7 +29690,7 @@
         <v>46193.393782037034</v>
       </c>
       <c r="D80" s="1">
-        <v>46193.64375</v>
+        <v>46193.39375</v>
       </c>
       <c r="E80">
         <v>22122</v>
@@ -29812,7 +29812,7 @@
         <v>46193.394125694445</v>
       </c>
       <c r="D81" s="1">
-        <v>46193.64409722222</v>
+        <v>46193.39409722222</v>
       </c>
       <c r="E81">
         <v>21627</v>
@@ -29934,7 +29934,7 @@
         <v>46193.39447263889</v>
       </c>
       <c r="D82" s="1">
-        <v>46193.64444444444</v>
+        <v>46193.39444444444</v>
       </c>
       <c r="E82">
         <v>21164</v>
@@ -30056,7 +30056,7 @@
         <v>46193.39482388889</v>
       </c>
       <c r="D83" s="1">
-        <v>46193.644791666666</v>
+        <v>46193.394791666666</v>
       </c>
       <c r="E83">
         <v>20695</v>
@@ -30178,7 +30178,7 @@
         <v>46193.395167800925</v>
       </c>
       <c r="D84" s="1">
-        <v>46193.64513888889</v>
+        <v>46193.39513888889</v>
       </c>
       <c r="E84">
         <v>20232</v>
@@ -30300,7 +30300,7 @@
         <v>46193.395514791664</v>
       </c>
       <c r="D85" s="1">
-        <v>46193.64548611111</v>
+        <v>46193.39548611111</v>
       </c>
       <c r="E85">
         <v>19806</v>
@@ -30422,7 +30422,7 @@
         <v>46193.39586560185</v>
       </c>
       <c r="D86" s="1">
-        <v>46193.645833333336</v>
+        <v>46193.395833333336</v>
       </c>
       <c r="E86">
         <v>19382</v>
@@ -30544,7 +30544,7 @@
         <v>46193.39620855324</v>
       </c>
       <c r="D87" s="1">
-        <v>46193.64618055556</v>
+        <v>46193.39618055556</v>
       </c>
       <c r="E87">
         <v>18953</v>
@@ -30666,7 +30666,7 @@
         <v>46193.39655621528</v>
       </c>
       <c r="D88" s="1">
-        <v>46193.646527777775</v>
+        <v>46193.396527777775</v>
       </c>
       <c r="E88">
         <v>18516</v>
@@ -30788,7 +30788,7 @@
         <v>46193.39690717593</v>
       </c>
       <c r="D89" s="1">
-        <v>46193.646875</v>
+        <v>46193.396875</v>
       </c>
       <c r="E89">
         <v>18080</v>
@@ -30910,7 +30910,7 @@
         <v>46193.3972509375</v>
       </c>
       <c r="D90" s="1">
-        <v>46193.64722222222</v>
+        <v>46193.39722222222</v>
       </c>
       <c r="E90">
         <v>17650</v>
@@ -31032,7 +31032,7 @@
         <v>46193.3975978125</v>
       </c>
       <c r="D91" s="1">
-        <v>46193.647569444445</v>
+        <v>46193.397569444445</v>
       </c>
       <c r="E91">
         <v>17213</v>
@@ -31154,7 +31154,7 @@
         <v>46193.39794930555</v>
       </c>
       <c r="D92" s="1">
-        <v>46193.64791666667</v>
+        <v>46193.39791666667</v>
       </c>
       <c r="E92">
         <v>16777</v>
@@ -31276,7 +31276,7 @@
         <v>46193.39829258102</v>
       </c>
       <c r="D93" s="1">
-        <v>46193.64826388889</v>
+        <v>46193.39826388889</v>
       </c>
       <c r="E93">
         <v>16341</v>
@@ -31398,7 +31398,7 @@
         <v>46193.398638680555</v>
       </c>
       <c r="D94" s="1">
-        <v>46193.64861111111</v>
+        <v>46193.39861111111</v>
       </c>
       <c r="E94">
         <v>15894</v>
@@ -31520,7 +31520,7 @@
         <v>46193.399337407405</v>
       </c>
       <c r="D95" s="1">
-        <v>46193.649305555555</v>
+        <v>46193.399305555555</v>
       </c>
       <c r="E95">
         <v>15022</v>
@@ -31642,7 +31642,7 @@
         <v>46193.39968099537</v>
       </c>
       <c r="D96" s="1">
-        <v>46193.64965277778</v>
+        <v>46193.39965277778</v>
       </c>
       <c r="E96">
         <v>14588</v>
@@ -31764,7 +31764,7 @@
         <v>46193.40002850694</v>
       </c>
       <c r="D97" s="1">
-        <v>46193.65</v>
+        <v>46193.4</v>
       </c>
       <c r="E97">
         <v>14165</v>
@@ -31886,7 +31886,7 @@
         <v>46193.40037883102</v>
       </c>
       <c r="D98" s="1">
-        <v>46193.650347222225</v>
+        <v>46193.400347222225</v>
       </c>
       <c r="E98">
         <v>13752</v>
@@ -32008,7 +32008,7 @@
         <v>46193.40072290509</v>
       </c>
       <c r="D99" s="1">
-        <v>46193.65069444444</v>
+        <v>46193.40069444444</v>
       </c>
       <c r="E99">
         <v>13342</v>
@@ -32130,7 +32130,7 @@
         <v>46193.401070011576</v>
       </c>
       <c r="D100" s="1">
-        <v>46193.651041666664</v>
+        <v>46193.401041666664</v>
       </c>
       <c r="E100">
         <v>12935</v>
@@ -32252,7 +32252,7 @@
         <v>46193.40142097222</v>
       </c>
       <c r="D101" s="1">
-        <v>46193.65138888889</v>
+        <v>46193.40138888889</v>
       </c>
       <c r="E101">
         <v>12531</v>
@@ -32374,7 +32374,7 @@
         <v>46193.401764664355</v>
       </c>
       <c r="D102" s="1">
-        <v>46193.65173611111</v>
+        <v>46193.40173611111</v>
       </c>
       <c r="E102">
         <v>12131</v>
@@ -32496,7 +32496,7 @@
         <v>46193.40211167824</v>
       </c>
       <c r="D103" s="1">
-        <v>46193.652083333334</v>
+        <v>46193.402083333334</v>
       </c>
       <c r="E103">
         <v>11730</v>
@@ -32618,7 +32618,7 @@
         <v>46193.40246251157</v>
       </c>
       <c r="D104" s="1">
-        <v>46193.65243055556</v>
+        <v>46193.40243055556</v>
       </c>
       <c r="E104">
         <v>11330</v>
@@ -32740,7 +32740,7 @@
         <v>46193.402805983795</v>
       </c>
       <c r="D105" s="1">
-        <v>46193.65277777778</v>
+        <v>46193.40277777778</v>
       </c>
       <c r="E105">
         <v>10923</v>
@@ -32862,7 +32862,7 @@
         <v>46193.40315318287</v>
       </c>
       <c r="D106" s="1">
-        <v>46193.653125</v>
+        <v>46193.403125</v>
       </c>
       <c r="E106">
         <v>10516</v>
@@ -32984,7 +32984,7 @@
         <v>46193.403503912035</v>
       </c>
       <c r="D107" s="1">
-        <v>46193.65347222222</v>
+        <v>46193.40347222222</v>
       </c>
       <c r="E107">
         <v>10100</v>
@@ -33106,7 +33106,7 @@
         <v>46193.403848043985</v>
       </c>
       <c r="D108" s="1">
-        <v>46193.653819444444</v>
+        <v>46193.403819444444</v>
       </c>
       <c r="E108">
         <v>9680</v>
@@ -33228,7 +33228,7 @@
         <v>46193.4041946412</v>
       </c>
       <c r="D109" s="1">
-        <v>46193.65416666667</v>
+        <v>46193.40416666667</v>
       </c>
       <c r="E109">
         <v>9247</v>
@@ -33350,7 +33350,7 @@
         <v>46193.4045453125</v>
       </c>
       <c r="D110" s="1">
-        <v>46193.65451388889</v>
+        <v>46193.40451388889</v>
       </c>
       <c r="E110">
         <v>8836</v>
@@ -33472,7 +33472,7 @@
         <v>46193.4048893287</v>
       </c>
       <c r="D111" s="1">
-        <v>46193.654861111114</v>
+        <v>46193.404861111114</v>
       </c>
       <c r="E111">
         <v>8436</v>
@@ -33594,7 +33594,7 @@
         <v>46193.405236527775</v>
       </c>
       <c r="D112" s="1">
-        <v>46193.65520833333</v>
+        <v>46193.40520833333</v>
       </c>
       <c r="E112">
         <v>8033</v>
@@ -33716,7 +33716,7 @@
         <v>46193.40558744213</v>
       </c>
       <c r="D113" s="1">
-        <v>46193.65555555555</v>
+        <v>46193.40555555555</v>
       </c>
       <c r="E113">
         <v>7619</v>
@@ -33838,7 +33838,7 @@
         <v>46193.40593126157</v>
       </c>
       <c r="D114" s="1">
-        <v>46193.65590277778</v>
+        <v>46193.40590277778</v>
       </c>
       <c r="E114">
         <v>7229</v>
@@ -33960,7 +33960,7 @@
         <v>46193.40627836806</v>
       </c>
       <c r="D115" s="1">
-        <v>46193.65625</v>
+        <v>46193.40625</v>
       </c>
       <c r="E115">
         <v>6848</v>
@@ -34082,7 +34082,7 @@
         <v>46193.40662902778</v>
       </c>
       <c r="D116" s="1">
-        <v>46193.65659722222</v>
+        <v>46193.40659722222</v>
       </c>
       <c r="E116">
         <v>6484</v>
@@ -34204,7 +34204,7 @@
         <v>46193.406972847224</v>
       </c>
       <c r="D117" s="1">
-        <v>46193.65694444445</v>
+        <v>46193.40694444445</v>
       </c>
       <c r="E117">
         <v>6146</v>
@@ -34326,7 +34326,7 @@
         <v>46193.407320439816</v>
       </c>
       <c r="D118" s="1">
-        <v>46193.65729166667</v>
+        <v>46193.40729166667</v>
       </c>
       <c r="E118">
         <v>5785</v>
@@ -34448,7 +34448,7 @@
         <v>46193.40767050926</v>
       </c>
       <c r="D119" s="1">
-        <v>46193.657638888886</v>
+        <v>46193.407638888886</v>
       </c>
       <c r="E119">
         <v>5450</v>
@@ -34570,7 +34570,7 @@
         <v>46193.40801453704</v>
       </c>
       <c r="D120" s="1">
-        <v>46193.65798611111</v>
+        <v>46193.40798611111</v>
       </c>
       <c r="E120">
         <v>5129</v>
@@ -34692,7 +34692,7 @@
         <v>46193.408361284724</v>
       </c>
       <c r="D121" s="1">
-        <v>46193.65833333333</v>
+        <v>46193.40833333333</v>
       </c>
       <c r="E121">
         <v>4797</v>
@@ -34814,7 +34814,7 @@
         <v>46193.40871263889</v>
       </c>
       <c r="D122" s="1">
-        <v>46193.658680555556</v>
+        <v>46193.408680555556</v>
       </c>
       <c r="E122">
         <v>4459</v>
@@ -34936,7 +34936,7 @@
         <v>46193.409055729164</v>
       </c>
       <c r="D123" s="1">
-        <v>46193.65902777778</v>
+        <v>46193.40902777778</v>
       </c>
       <c r="E123">
         <v>4128</v>
@@ -35058,7 +35058,7 @@
         <v>46193.409403819445</v>
       </c>
       <c r="D124" s="1">
-        <v>46193.659375</v>
+        <v>46193.409375</v>
       </c>
       <c r="E124">
         <v>3803</v>
@@ -35180,7 +35180,7 @@
         <v>46193.40975394676</v>
       </c>
       <c r="D125" s="1">
-        <v>46193.65972222222</v>
+        <v>46193.40972222222</v>
       </c>
       <c r="E125">
         <v>3475</v>
@@ -35302,7 +35302,7 @@
         <v>46193.41009806713</v>
       </c>
       <c r="D126" s="1">
-        <v>46193.66006944444</v>
+        <v>46193.41006944444</v>
       </c>
       <c r="E126">
         <v>3160</v>
@@ -35424,7 +35424,7 @@
         <v>46193.41044513889</v>
       </c>
       <c r="D127" s="1">
-        <v>46193.660416666666</v>
+        <v>46193.410416666666</v>
       </c>
       <c r="E127">
         <v>2819</v>
@@ -35546,7 +35546,7 @@
         <v>46193.41079589121</v>
       </c>
       <c r="D128" s="1">
-        <v>46193.66076388889</v>
+        <v>46193.41076388889</v>
       </c>
       <c r="E128">
         <v>2461</v>
@@ -35668,7 +35668,7 @@
         <v>46193.411139351854</v>
       </c>
       <c r="D129" s="1">
-        <v>46193.66111111111</v>
+        <v>46193.41111111111</v>
       </c>
       <c r="E129">
         <v>2116</v>
@@ -35790,7 +35790,7 @@
         <v>46193.41148700231</v>
       </c>
       <c r="D130" s="1">
-        <v>46193.661458333336</v>
+        <v>46193.411458333336</v>
       </c>
       <c r="E130">
         <v>1782</v>
@@ -35912,7 +35912,7 @@
         <v>46193.41183755787</v>
       </c>
       <c r="D131" s="1">
-        <v>46193.66180555556</v>
+        <v>46193.41180555556</v>
       </c>
       <c r="E131">
         <v>1473</v>
@@ -36034,7 +36034,7 @@
         <v>46193.41218126158</v>
       </c>
       <c r="D132" s="1">
-        <v>46193.662152777775</v>
+        <v>46193.412152777775</v>
       </c>
       <c r="E132">
         <v>1148</v>
@@ -36156,7 +36156,7 @@
         <v>46193.412528622684</v>
       </c>
       <c r="D133" s="1">
-        <v>46193.6625</v>
+        <v>46193.4125</v>
       </c>
       <c r="E133">
         <v>850</v>
@@ -36278,7 +36278,7 @@
         <v>46193.41287949074</v>
       </c>
       <c r="D134" s="1">
-        <v>46193.66284722222</v>
+        <v>46193.41284722222</v>
       </c>
       <c r="E134">
         <v>732</v>
